--- a/批量添加道具-毛茸清单.xlsx
+++ b/批量添加道具-毛茸清单.xlsx
@@ -66,7 +66,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -78,6 +78,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -419,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11" defaultRowHeight="15.5"/>
   <cols>
     <col width="29.4609375" customWidth="1" style="3" min="1" max="1"/>
@@ -482,277 +485,427 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="0" t="inlineStr">
         <is>
           <t>zodiac_taurus</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="0" t="inlineStr">
         <is>
           <t>金牛</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="0" t="inlineStr">
         <is>
           <t>https://cloud1-d4gck1kjyb8ca2456.service.tcloudbase.com/propImages?name=zodiac_taurus</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>6</v>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="D3" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="E3" s="0" t="inlineStr">
         <is>
           <t>星座宠物形象</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="0" t="inlineStr">
         <is>
           <t>zodiac_gemini</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="0" t="inlineStr">
         <is>
           <t>双子</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="0" t="inlineStr">
         <is>
           <t>https://cloud1-d4gck1kjyb8ca2456.service.tcloudbase.com/propImages?name=zodiac_gemini</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>6</v>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="D4" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="E4" s="0" t="inlineStr">
         <is>
           <t>星座宠物形象</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="0" t="inlineStr">
         <is>
           <t>zodiac_cancer</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="0" t="inlineStr">
         <is>
           <t>巨蟹</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="0" t="inlineStr">
         <is>
           <t>https://cloud1-d4gck1kjyb8ca2456.service.tcloudbase.com/propImages?name=zodiac_cancer</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>6</v>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="D5" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="E5" s="0" t="inlineStr">
         <is>
           <t>星座宠物形象</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="0" t="inlineStr">
         <is>
           <t>zodiac_leo</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="0" t="inlineStr">
         <is>
           <t>狮子</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="0" t="inlineStr">
         <is>
           <t>https://cloud1-d4gck1kjyb8ca2456.service.tcloudbase.com/propImages?name=zodiac_leo</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>6</v>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="D6" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="E6" s="0" t="inlineStr">
         <is>
           <t>星座宠物形象</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="0" t="inlineStr">
         <is>
           <t>zodiac_virgo</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="0" t="inlineStr">
         <is>
           <t>处女</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="0" t="inlineStr">
         <is>
           <t>https://cloud1-d4gck1kjyb8ca2456.service.tcloudbase.com/propImages?name=zodiac_virgo</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>6</v>
-      </c>
-      <c r="E7" t="inlineStr">
+      <c r="D7" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="E7" s="0" t="inlineStr">
         <is>
           <t>星座宠物形象</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="0" t="inlineStr">
         <is>
           <t>zodiac_libra</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="0" t="inlineStr">
         <is>
           <t>天秤</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="0" t="inlineStr">
         <is>
           <t>https://cloud1-d4gck1kjyb8ca2456.service.tcloudbase.com/propImages?name=zodiac_libra</t>
         </is>
       </c>
-      <c r="D8" t="n">
-        <v>6</v>
-      </c>
-      <c r="E8" t="inlineStr">
+      <c r="D8" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="E8" s="0" t="inlineStr">
         <is>
           <t>星座宠物形象</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="0" t="inlineStr">
         <is>
           <t>zodiac_scorpio</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="0" t="inlineStr">
         <is>
           <t>天蝎</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="0" t="inlineStr">
         <is>
           <t>https://cloud1-d4gck1kjyb8ca2456.service.tcloudbase.com/propImages?name=zodiac_scorpio</t>
         </is>
       </c>
-      <c r="D9" t="n">
-        <v>6</v>
-      </c>
-      <c r="E9" t="inlineStr">
+      <c r="D9" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="E9" s="0" t="inlineStr">
         <is>
           <t>星座宠物形象</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="0" t="inlineStr">
         <is>
           <t>zodiac_sagittarius</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="0" t="inlineStr">
         <is>
           <t>射手</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="0" t="inlineStr">
         <is>
           <t>https://cloud1-d4gck1kjyb8ca2456.service.tcloudbase.com/propImages?name=zodiac_sagittarius</t>
         </is>
       </c>
-      <c r="D10" t="n">
-        <v>6</v>
-      </c>
-      <c r="E10" t="inlineStr">
+      <c r="D10" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="E10" s="0" t="inlineStr">
         <is>
           <t>星座宠物形象</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="0" t="inlineStr">
         <is>
           <t>zodiac_capricorn</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="0" t="inlineStr">
         <is>
           <t>摩羯</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="0" t="inlineStr">
         <is>
           <t>https://cloud1-d4gck1kjyb8ca2456.service.tcloudbase.com/propImages?name=zodiac_capricorn</t>
         </is>
       </c>
-      <c r="D11" t="n">
-        <v>6</v>
-      </c>
-      <c r="E11" t="inlineStr">
+      <c r="D11" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="E11" s="0" t="inlineStr">
         <is>
           <t>星座宠物形象</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="0" t="inlineStr">
         <is>
           <t>zodiac_aquarius</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="0" t="inlineStr">
         <is>
           <t>水瓶</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="0" t="inlineStr">
         <is>
           <t>https://cloud1-d4gck1kjyb8ca2456.service.tcloudbase.com/propImages?name=zodiac_aquarius</t>
         </is>
       </c>
-      <c r="D12" t="n">
-        <v>6</v>
-      </c>
-      <c r="E12" t="inlineStr">
+      <c r="D12" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="E12" s="0" t="inlineStr">
         <is>
           <t>星座宠物形象</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="0" t="inlineStr">
         <is>
           <t>zodiac_pisces</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="0" t="inlineStr">
         <is>
           <t>双鱼</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="0" t="inlineStr">
         <is>
           <t>https://cloud1-d4gck1kjyb8ca2456.service.tcloudbase.com/propImages?name=zodiac_pisces</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>6</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>星座宠物形象</t>
+      <c r="D13" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="E13" s="0" t="inlineStr">
+        <is>
+          <t>星座宠物形象</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="inlineStr">
+        <is>
+          <t>zodiac_bundle_0</t>
+        </is>
+      </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>全家桶补36元</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>https://cloud1-d4gck1kjyb8ca2456.service.tcloudbase.com/propImages?name=zodiac_bundle</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="E14" s="0" t="inlineStr">
+        <is>
+          <t>全家桶：一次买断剩余 12 只星座宠物（封顶 ¥36）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="inlineStr">
+        <is>
+          <t>zodiac_bundle_1</t>
+        </is>
+      </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>全家桶补30元</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>https://cloud1-d4gck1kjyb8ca2456.service.tcloudbase.com/propImages?name=zodiac_bundle</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="E15" s="0" t="inlineStr">
+        <is>
+          <t>全家桶：一次买断剩余 11 只星座宠物（封顶 ¥36）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="inlineStr">
+        <is>
+          <t>zodiac_bundle_2</t>
+        </is>
+      </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t>全家桶补24元</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>https://cloud1-d4gck1kjyb8ca2456.service.tcloudbase.com/propImages?name=zodiac_bundle</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="E16" s="0" t="inlineStr">
+        <is>
+          <t>全家桶：一次买断剩余 10 只星座宠物（封顶 ¥36）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="inlineStr">
+        <is>
+          <t>zodiac_bundle_3</t>
+        </is>
+      </c>
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>全家桶补18元</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>https://cloud1-d4gck1kjyb8ca2456.service.tcloudbase.com/propImages?name=zodiac_bundle</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="E17" s="0" t="inlineStr">
+        <is>
+          <t>全家桶：一次买断剩余 9 只星座宠物（封顶 ¥36）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0" t="inlineStr">
+        <is>
+          <t>zodiac_bundle_4</t>
+        </is>
+      </c>
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t>全家桶补12元</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>https://cloud1-d4gck1kjyb8ca2456.service.tcloudbase.com/propImages?name=zodiac_bundle</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="E18" s="0" t="inlineStr">
+        <is>
+          <t>全家桶：一次买断剩余 8 只星座宠物（封顶 ¥36）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="0" t="inlineStr">
+        <is>
+          <t>zodiac_bundle_5</t>
+        </is>
+      </c>
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>全家桶补6元</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>https://cloud1-d4gck1kjyb8ca2456.service.tcloudbase.com/propImages?name=zodiac_bundle</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E19" s="0" t="inlineStr">
+        <is>
+          <t>全家桶：一次买断剩余 7 只星座宠物（封顶 ¥36）</t>
         </is>
       </c>
     </row>
